--- a/SDWAN Installation Tracker Master User Data.xlsx
+++ b/SDWAN Installation Tracker Master User Data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CORE_CONTENT\CODE\dir_root_ITrack\static\scripts\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CORE_CONTENT\CODE\dir_root_ITrack\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABB0F8D0-8F36-43F0-96A6-8334CC347673}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{865FDDFE-5161-45CD-9001-8174A59FE4AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{06F2C58F-538C-42BA-94BB-563052BD2C07}"/>
   </bookViews>
